--- a/product_upload/packages/14/file.xlsx
+++ b/product_upload/packages/14/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -840,6 +845,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>CEFIM 200MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-C94DC5936073</t>
         </is>
       </c>
@@ -863,7 +873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1034,6 +1044,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>CEFIX 400MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-A0502A08B8F7</t>
         </is>
       </c>
@@ -1057,7 +1072,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1224,6 +1239,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>CIPROXEN 500MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-B4A3DCF70CF9</t>
         </is>
       </c>
@@ -1247,7 +1267,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1414,6 +1434,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>CERAZETTE 75MCG TAB</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-9704FD2DCF12</t>
         </is>
       </c>
@@ -1437,7 +1462,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1604,6 +1629,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>CIPROGEN</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-C94C05FA7F13</t>
         </is>
       </c>
@@ -1627,7 +1657,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1786,6 +1816,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>CIPROFLACIN 500 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-7889ECE818A2</t>
         </is>
       </c>
@@ -1809,7 +1844,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1980,6 +2015,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>CIPROCIN 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-F8CE55CEAC7F</t>
         </is>
       </c>
@@ -2003,7 +2043,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2166,6 +2206,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>CIPROCIN 250MG TAB</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-C34959DA4A84</t>
         </is>
       </c>
@@ -2189,7 +2234,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2356,6 +2401,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>CIPROCIN 0.3%</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-5BF2E43D1457</t>
         </is>
       </c>
@@ -2379,7 +2429,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2544,6 +2594,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>CIPROBAY 750MG TAB</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-24FC7DB26258</t>
         </is>
       </c>
@@ -2567,7 +2622,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2740,6 +2795,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>CIPROBAY 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-AD59C5D7A458</t>
         </is>
       </c>
@@ -2763,7 +2823,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2924,6 +2984,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>CIPROBAY 250MG TAB</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-35B84BE5FB47</t>
         </is>
       </c>
@@ -2947,7 +3012,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3110,6 +3175,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>CIPROHEXAL 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-6C18A6164810</t>
         </is>
       </c>
@@ -3133,7 +3203,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3300,6 +3370,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>CIPROHEXAL 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-12745296A5E4</t>
         </is>
       </c>
@@ -3323,7 +3398,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3482,6 +3557,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>CIPROLET 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-6D550A462568</t>
         </is>
       </c>
@@ -3505,7 +3585,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3668,6 +3748,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>CIPROQUIN</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-619B210D04B4</t>
         </is>
       </c>
@@ -3691,7 +3776,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3866,6 +3951,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>CIPROPHARM 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-484F410B5D81</t>
         </is>
       </c>
@@ -3889,7 +3979,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4052,6 +4142,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>CIPROMID 750MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-712897943F43</t>
         </is>
       </c>
@@ -4075,7 +4170,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4242,6 +4337,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>CIPROMID 500MG F-C TABLET</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-FDCF85E7B582</t>
         </is>
       </c>
@@ -4265,7 +4365,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4432,6 +4532,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>CIPROMID 250MG F-C TABLET</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-732A34A5E907</t>
         </is>
       </c>
@@ -4455,7 +4560,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4622,6 +4727,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>CIPROMAX 500 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-7BE4F62680FC</t>
         </is>
       </c>
@@ -4645,7 +4755,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4808,6 +4918,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CIPROLET 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-6F08C01DFBFA</t>
         </is>
       </c>
@@ -4831,7 +4946,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5002,6 +5117,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>CIPROMAX 750MG TAB</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-B9EAB9B31A16</t>
         </is>
       </c>
@@ -5025,7 +5145,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5196,6 +5316,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>CIPRAM 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-2605C8BAA5B5</t>
         </is>
       </c>
@@ -5219,7 +5344,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5382,6 +5507,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>CIFLOX 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-B1A8D735D8A2</t>
         </is>
       </c>
@@ -5405,7 +5535,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5576,6 +5706,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>CETROTIDE 0.25MG POW. FOR SOLU. FOR INJ.</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-3CB88A948ADC</t>
         </is>
       </c>
@@ -5599,7 +5734,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5754,6 +5889,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>CEREPAR</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-44FFEF2B1A32</t>
         </is>
       </c>
@@ -5777,7 +5917,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5940,6 +6080,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>CEREPAR</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-09DCC46E3AB9</t>
         </is>
       </c>
@@ -5963,7 +6108,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6126,6 +6271,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>CEVITAN EFFERVESCENT TAB</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-79C345D75659</t>
         </is>
       </c>
@@ -6149,7 +6299,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6312,6 +6462,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>CEVITIL 1 g effervescent tablet</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-50D6BCD22C28</t>
         </is>
       </c>
@@ -6335,7 +6490,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6494,6 +6649,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>CHAMPIX 0.5 MG F-C TAB</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-608FE7EF291C</t>
         </is>
       </c>
@@ -6517,7 +6677,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6680,6 +6840,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>CIFLOX 250MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-24C26898193B</t>
         </is>
       </c>
@@ -6703,7 +6868,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6878,6 +7043,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>CHORIOMON 5000 I.U VIAL+AMP OF SOLVENT</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-555FDB7B6A6A</t>
         </is>
       </c>
@@ -6901,7 +7071,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7068,6 +7238,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>CHLOROQUINE</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-8D53E224EE1F</t>
         </is>
       </c>
@@ -7091,7 +7266,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7258,6 +7433,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>CHLOROQUINE</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-AC5013889044</t>
         </is>
       </c>
@@ -7281,7 +7461,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7452,6 +7632,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>CHAMPIX 1MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-836F9AE03517</t>
         </is>
       </c>
@@ -7475,7 +7660,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7646,6 +7831,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>CHAMPIX 1MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-BFF381CB44F3</t>
         </is>
       </c>
@@ -7669,7 +7859,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7832,6 +8022,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>CHAMPIX 0.5 MG 11 tablets +1 MG 14 tablets</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-53210341892F</t>
         </is>
       </c>
@@ -7855,7 +8050,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8028,6 +8223,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>COVERSYL 10MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-355B42C38318</t>
         </is>
       </c>
@@ -8051,7 +8251,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8220,6 +8420,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>COVERSYL 5MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-C14417488CD0</t>
         </is>
       </c>
@@ -8243,7 +8448,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8406,6 +8611,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-C7183487E7E0</t>
         </is>
       </c>
@@ -8429,7 +8639,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8592,6 +8802,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-6140BAE318AC</t>
         </is>
       </c>
@@ -8615,7 +8830,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8778,6 +8993,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-1051D2F3388F</t>
         </is>
       </c>
@@ -8801,7 +9021,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8960,6 +9180,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-F11A9C491DBB</t>
         </is>
       </c>
@@ -8983,7 +9208,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9142,6 +9367,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>10% Dextrose intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-F0FCBE75C108</t>
         </is>
       </c>
@@ -9165,7 +9395,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9320,6 +9550,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-A8EE3672F5C1</t>
         </is>
       </c>
@@ -9343,7 +9578,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9502,6 +9737,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>DEXTROSE 10%</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-EF16CAEDC6CD</t>
         </is>
       </c>
@@ -9525,7 +9765,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9688,6 +9928,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>DEXTROSE 10%</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-4891C52B2F64</t>
         </is>
       </c>
@@ -9711,7 +9956,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9870,6 +10115,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>DEXTROSE 10%</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-2C335C47E9A9</t>
         </is>
       </c>
@@ -9893,7 +10143,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10056,6 +10306,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>DEXTROSE +SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-5D954C53AFCF</t>
         </is>
       </c>
@@ -10079,7 +10334,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10234,6 +10489,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>DEXTROSE +LACTATED RINGER</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-DD6B7E04B713</t>
         </is>
       </c>
@@ -10257,7 +10517,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10416,6 +10676,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>DEXTROSE +LACTATED RINGER</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-7B9434346E68</t>
         </is>
       </c>
@@ -10439,7 +10704,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10602,6 +10867,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>DEXTROSE +LACTATED RINGER</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-8A7FD2267778</t>
         </is>
       </c>
@@ -10625,7 +10895,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10784,6 +11054,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>DEXTROSE +LACTATED RINGER</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-F5B83862ED8B</t>
         </is>
       </c>
@@ -10807,7 +11082,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10974,6 +11249,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-7D09D72C60EE</t>
         </is>
       </c>
@@ -10997,7 +11277,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11156,6 +11436,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-3058A05C3BB9</t>
         </is>
       </c>
@@ -11179,7 +11464,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11342,6 +11627,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% IN 1-2 NORMAL SALINE</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-1571C2F628E2</t>
         </is>
       </c>
@@ -11365,7 +11655,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11532,6 +11822,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% IN 1-2 NORMAL SALINE</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-535CE865C3B0</t>
         </is>
       </c>
@@ -11555,7 +11850,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11722,6 +12017,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% IN 1-2 NORMAL SALINE</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-49F352B73287</t>
         </is>
       </c>
@@ -11745,7 +12045,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11908,6 +12208,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>DEXTROSE 10%+ SOD.CHLORIDE 0.18%</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-6D3793CC6DB7</t>
         </is>
       </c>
@@ -11931,7 +12236,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12090,6 +12395,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% SOLUTION FOR INJ</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-125314D3DE22</t>
         </is>
       </c>
@@ -12113,7 +12423,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12272,6 +12582,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-BC7773F2C6F5</t>
         </is>
       </c>
@@ -12295,7 +12610,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12462,6 +12777,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% IN0.225% SOD.CHLORIDE INFS</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-4AA066BDF5AF</t>
         </is>
       </c>
@@ -12485,7 +12805,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12652,6 +12972,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% IN0.225% SOD.CHLORIDE INFS</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-89912B35ECCD</t>
         </is>
       </c>
@@ -12675,7 +13000,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12842,6 +13167,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% IN0.225% SOD.CHLORIDE INFS</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-B6F2A102D4B2</t>
         </is>
       </c>
@@ -12865,7 +13195,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13032,6 +13362,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% IN 1-5NORMAL SALINE INFUSIO</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-74A1DC402329</t>
         </is>
       </c>
@@ -13055,7 +13390,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13218,6 +13553,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>DEXTROSE 10% IN 1-5NORMAL SALINE INFUSIO</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-1C18EA5308BD</t>
         </is>
       </c>
@@ -13241,7 +13581,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13408,6 +13748,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>DEXTROSE 10%+ SOD.CHLORIDE 0.18%</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-7A46A71BE3BD</t>
         </is>
       </c>
@@ -13431,7 +13776,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13598,6 +13943,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-DAF0BCA715EA</t>
         </is>
       </c>
@@ -13621,7 +13971,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13784,6 +14134,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-5B350FC475D8</t>
         </is>
       </c>
@@ -13807,7 +14162,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13966,6 +14321,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>DEXTROSE ,RINGER LACTATE</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-E9038B455BCF</t>
         </is>
       </c>
@@ -13989,7 +14349,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14148,6 +14508,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>DEXTROSE ,RINGER</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-68A5F3531037</t>
         </is>
       </c>
@@ -14171,7 +14536,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14330,6 +14695,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>DEXTROSE ,RINGER</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-2D14B3CE99D1</t>
         </is>
       </c>
@@ -14353,7 +14723,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14512,6 +14882,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>DEXTROSE ,RINGER</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-2191DCEC8367</t>
         </is>
       </c>
@@ -14535,7 +14910,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14706,6 +15081,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>DEXTROKUF 15MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-4A7D9814FA71</t>
         </is>
       </c>
@@ -14729,7 +15109,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14888,6 +15268,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>DEXTROSE ,RINGER LACTATE</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-CE9555397FA5</t>
         </is>
       </c>
@@ -14911,7 +15296,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15070,6 +15455,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>DEXTROSE ,RINGER LACTATE</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-01C07AAC1FAD</t>
         </is>
       </c>
@@ -15093,7 +15483,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15260,6 +15650,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-78613285C42D</t>
         </is>
       </c>
@@ -15283,7 +15678,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15446,6 +15841,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-A8FF99573966</t>
         </is>
       </c>
@@ -15469,7 +15869,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15632,6 +16032,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-0A0F0FCEDF4E</t>
         </is>
       </c>
@@ -15655,7 +16060,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15814,6 +16219,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-29DB7792381E</t>
         </is>
       </c>
@@ -15837,7 +16247,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16000,6 +16410,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-6E63733DD22E</t>
         </is>
       </c>
@@ -16023,7 +16438,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16190,6 +16605,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-C24C82C8C776</t>
         </is>
       </c>
@@ -16213,7 +16633,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16380,6 +16800,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-40612D403818</t>
         </is>
       </c>
@@ -16403,7 +16828,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16570,6 +16995,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-DB312C85C6A9</t>
         </is>
       </c>
@@ -16593,7 +17023,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16760,6 +17190,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-70EF9E83329B</t>
         </is>
       </c>
@@ -16783,7 +17218,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16950,6 +17385,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-DD10B333E2BB</t>
         </is>
       </c>
@@ -16973,7 +17413,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17140,6 +17580,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-E5A75ADB06E4</t>
         </is>
       </c>
@@ -17163,7 +17608,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17330,6 +17775,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-148229829912</t>
         </is>
       </c>
@@ -17353,7 +17803,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17516,6 +17966,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-7B62D2C025F8</t>
         </is>
       </c>
@@ -17539,7 +17994,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17706,6 +18161,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-486E3ACA539A</t>
         </is>
       </c>
@@ -17729,7 +18189,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17892,6 +18352,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-906363B64401</t>
         </is>
       </c>
@@ -17915,7 +18380,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18078,6 +18543,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-19849B250C1C</t>
         </is>
       </c>
@@ -18101,7 +18571,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18268,6 +18738,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-A3ED31E2A762</t>
         </is>
       </c>
@@ -18291,7 +18766,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18458,6 +18933,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-EBEE2CD69B0A</t>
         </is>
       </c>
@@ -18481,7 +18961,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18644,6 +19124,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-97CE08BCFD2C</t>
         </is>
       </c>
@@ -18667,7 +19152,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18830,6 +19315,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>DEXTROSE 10%+ SOD.CHLORIDE 0.18%</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-50AB303CC866</t>
         </is>
       </c>
@@ -18853,7 +19343,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19020,6 +19510,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>DEXTROSE 10%+N.SALINE INJ</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-1871EF6F4F21</t>
         </is>
       </c>
@@ -19043,7 +19538,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19202,6 +19697,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% IN 0.45% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-360416A0CBD6</t>
         </is>
       </c>
@@ -19225,7 +19725,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19383,6 +19883,11 @@
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% IN 0.45% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-464937465EAB</t>
         </is>
@@ -19399,7 +19904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19445,100 +19950,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19570,7 +20080,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19585,92 +20095,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-39523</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>208.76</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>49</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19702,7 +20217,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19717,92 +20232,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-83817</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>306.1</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>50</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19834,7 +20354,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19849,92 +20369,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-87243</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>223.55</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>51</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19966,7 +20491,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19981,92 +20506,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-10314</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>483.03</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>52</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20098,7 +20628,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20113,92 +20643,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-13171</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>96.66</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>53</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20230,7 +20765,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20245,92 +20780,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-30844</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>233.21</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>54</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20362,7 +20902,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20377,92 +20917,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-24908</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>438.95</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>55</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20494,7 +21039,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20509,92 +21054,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-56230</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>323.17</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>56</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20626,7 +21176,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20641,92 +21191,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-41983</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>382.92</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>57</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20758,7 +21313,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20773,92 +21328,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-67696</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>137.24</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>58</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20890,7 +21450,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20905,92 +21465,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-54042</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>87.89</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>59</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21022,7 +21587,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21037,92 +21602,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-45932</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>130.63</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>60</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21139,7 +21709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21245,6 +21815,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21280,7 +21860,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21345,6 +21925,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-04CDB5F12AA3</t>
         </is>
@@ -21381,7 +21971,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21446,6 +22036,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-80EEDD35058A</t>
         </is>
@@ -21482,7 +22082,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21547,6 +22147,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-051B5F81505B</t>
         </is>
@@ -21583,7 +22193,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21648,6 +22258,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-3CC43E490579</t>
         </is>
@@ -21684,7 +22304,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21749,6 +22369,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-A97355E4C837</t>
         </is>
@@ -21785,7 +22415,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21850,6 +22480,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-5B35969A6175</t>
         </is>
@@ -21886,7 +22526,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21951,6 +22591,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-1BA60D0A1548</t>
         </is>
@@ -21987,7 +22637,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22052,6 +22702,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-0836F2B8CB63</t>
         </is>
@@ -22088,7 +22748,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22153,6 +22813,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-A318F0F1AAD4</t>
         </is>
@@ -22189,7 +22859,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22254,6 +22924,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-1AF8D513017F</t>
         </is>
@@ -22290,7 +22970,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22355,6 +23035,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-567917B5C0A9</t>
         </is>
@@ -22391,7 +23081,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22456,6 +23146,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-EE0867B1ED6C</t>
         </is>
@@ -22492,7 +23192,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22557,6 +23257,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-CA8CDF4B989D</t>
         </is>
@@ -22593,7 +23303,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22658,6 +23368,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-B70E08DB07FB</t>
         </is>
@@ -22694,7 +23414,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22759,6 +23479,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-AA68F2A443C6</t>
         </is>
@@ -22795,7 +23525,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22860,6 +23590,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-4E298F5E2455</t>
         </is>
@@ -22896,7 +23636,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22961,6 +23701,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-4753B2AD06A3</t>
         </is>
@@ -22997,7 +23747,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23062,6 +23812,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-D0FC4C62AAFD</t>
         </is>
@@ -23098,7 +23858,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23163,6 +23923,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-42AC39CB6C72</t>
         </is>
@@ -23199,7 +23969,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23264,6 +24034,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-D7205CAFC64A</t>
         </is>

--- a/product_upload/packages/14/file.xlsx
+++ b/product_upload/packages/14/file.xlsx
@@ -1665,8 +1665,16 @@
           <t>3732858675-344-930619069271</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROFLACIN 500 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CIPROFLACIN 500 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2051,8 +2059,16 @@
           <t>4790882167-100-924041972563</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROCIN 250MG TAB</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CIPROCIN 250MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2437,8 +2453,16 @@
           <t>0751255743-670-585319874126</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROBAY 750MG TAB</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CIPROBAY 750MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>DEEF PHARMACEUTICAL INDUSTRIES</t>
@@ -2831,8 +2855,16 @@
           <t>9114345196-048-718902618530</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROBAY 250MG TAB</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CIPROBAY 250MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>DEEF PHARMACEUTICAL INDUSTRIES</t>
@@ -3020,8 +3052,16 @@
           <t>8361438039-315-651833499564</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROHEXAL 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CIPROHEXAL 250MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3211,8 +3251,16 @@
           <t>2627267189-637-762492231014</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROHEXAL 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CIPROHEXAL 500MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3406,8 +3454,16 @@
           <t>1233902536-331-162410282528</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROLET 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CIPROLET 250MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3593,8 +3649,16 @@
           <t>6798602345-881-537594054428</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROQUIN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CIPROQUIN detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3987,8 +4051,16 @@
           <t>6889982560-528-358537902765</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROMID 750MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CIPROMID 750MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4178,8 +4250,16 @@
           <t>0176228130-972-356246537465</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROMID 500MG F-C TABLET</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CIPROMID 500MG F-C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4373,8 +4453,16 @@
           <t>0933215873-945-286286856300</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROMID 250MG F-C TABLET</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CIPROMID 250MG F-C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4763,8 +4851,16 @@
           <t>4514078301-195-445729103777</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROLET 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CIPROLET 500MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5352,8 +5448,16 @@
           <t>2376182719-471-635038942911</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIFLOX 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CIFLOX 500MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5742,8 +5846,16 @@
           <t>9193881590-595-192891083383</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEREPAR</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CEREPAR detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5925,8 +6037,16 @@
           <t>2919750021-170-098038426222</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEREPAR</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CEREPAR detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6116,8 +6236,16 @@
           <t>2378200777-049-671712072685</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEVITAN EFFERVESCENT TAB</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CEVITAN EFFERVESCENT TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6498,8 +6626,16 @@
           <t>2070846355-169-997357912795</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CHAMPIX 0.5 MG F-C TAB</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CHAMPIX 0.5 MG F-C TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6685,8 +6821,16 @@
           <t>3550652239-509-879679082256</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIFLOX 250MG TABLET</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CIFLOX 250MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -8456,8 +8600,16 @@
           <t>3099629867-878-638004625195</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% I.V.INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8647,8 +8799,16 @@
           <t>0736597200-990-186708747144</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% I.V.INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8838,8 +8998,16 @@
           <t>2582051160-889-991273613513</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% I.V.INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9029,8 +9197,16 @@
           <t>7083711518-111-329386384498</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% I.V.INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9216,8 +9392,16 @@
           <t>4393479415-002-648189644556</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 10% Dextrose intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>10% Dextrose intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9403,8 +9587,16 @@
           <t>7707289193-399-740544061164</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% I.V.INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9586,8 +9778,16 @@
           <t>1155303344-426-293764336205</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9773,8 +9973,16 @@
           <t>0294359811-741-878465705217</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9964,8 +10172,16 @@
           <t>1468759688-294-141755775780</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10151,8 +10367,16 @@
           <t>4330433911-522-608270147687</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE +SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>DEXTROSE +SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10342,8 +10566,16 @@
           <t>6757273737-936-976646480614</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE +LACTATED RINGER</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>DEXTROSE +LACTATED RINGER detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10525,8 +10757,16 @@
           <t>4532712728-314-212190718691</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE +LACTATED RINGER</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>DEXTROSE +LACTATED RINGER detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10712,8 +10952,16 @@
           <t>7523764707-254-677152348734</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE +LACTATED RINGER</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>DEXTROSE +LACTATED RINGER detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10903,8 +11151,16 @@
           <t>6789117396-218-373719171600</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE +LACTATED RINGER</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>DEXTROSE +LACTATED RINGER detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11090,8 +11346,16 @@
           <t>8266170020-513-246972300588</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>DEXTROSE + SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11285,8 +11549,16 @@
           <t>4299723260-810-277824531819</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% I.V.INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11472,8 +11744,16 @@
           <t>6128978907-541-632515107349</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% IN 1-2 NORMAL SALINE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% IN 1-2 NORMAL SALINE detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11663,8 +11943,16 @@
           <t>9633884225-802-134314914271</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% IN 1-2 NORMAL SALINE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% IN 1-2 NORMAL SALINE detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11858,8 +12146,16 @@
           <t>6519090284-644-412302950470</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% IN 1-2 NORMAL SALINE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% IN 1-2 NORMAL SALINE detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12053,8 +12349,16 @@
           <t>4734022794-402-316721500502</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10%+ SOD.CHLORIDE 0.18%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10%+ SOD.CHLORIDE 0.18% detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12244,8 +12548,16 @@
           <t>3868105219-504-299478643469</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% SOLUTION FOR INJ</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% SOLUTION FOR INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12431,8 +12743,16 @@
           <t>2497107141-044-210519670725</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>DEXTROSE + SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12618,8 +12938,16 @@
           <t>2453038866-800-847599037677</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% IN0.225% SOD.CHLORIDE INFS</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% IN0.225% SOD.CHLORIDE INFS detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12813,8 +13141,16 @@
           <t>3311609248-051-259325067239</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% IN0.225% SOD.CHLORIDE INFS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% IN0.225% SOD.CHLORIDE INFS detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13008,8 +13344,16 @@
           <t>2204452611-823-407052284861</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% IN0.225% SOD.CHLORIDE INFS</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% IN0.225% SOD.CHLORIDE INFS detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13203,8 +13547,16 @@
           <t>4667826964-296-457297221114</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% IN 1-5NORMAL SALINE INFUSIO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% IN 1-5NORMAL SALINE INFUSIO detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13398,8 +13750,16 @@
           <t>4962879887-304-976752159063</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10% IN 1-5NORMAL SALINE INFUSIO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10% IN 1-5NORMAL SALINE INFUSIO detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13589,8 +13949,16 @@
           <t>6913713175-157-952927099159</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10%+ SOD.CHLORIDE 0.18%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10%+ SOD.CHLORIDE 0.18% detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13784,8 +14152,16 @@
           <t>7985244215-369-351045997759</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>DEXTROSE + SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13979,8 +14355,16 @@
           <t>7085692480-281-325312407271</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>DEXTROSE + SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14170,8 +14554,16 @@
           <t>9279152065-934-923776299200</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,RINGER LACTATE</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,RINGER LACTATE detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14357,8 +14749,16 @@
           <t>6644014029-615-360661669613</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,RINGER</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,RINGER detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14544,8 +14944,16 @@
           <t>8575409732-280-086206425016</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,RINGER</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,RINGER detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14731,8 +15139,16 @@
           <t>7916207341-747-776977697594</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,RINGER</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,RINGER detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15117,8 +15533,16 @@
           <t>7830679940-241-795153837751</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,RINGER LACTATE</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,RINGER LACTATE detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15304,8 +15728,16 @@
           <t>6778431369-748-137450371247</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,RINGER LACTATE</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,RINGER LACTATE detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15491,8 +15923,16 @@
           <t>4400396170-381-964373804364</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15686,8 +16126,16 @@
           <t>7516422060-561-285728039816</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15877,8 +16325,16 @@
           <t>3712472422-210-587879325274</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>DEXTROSE + SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16068,8 +16524,16 @@
           <t>3361250470-865-013652458161</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>DEXTROSE + SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16255,8 +16719,16 @@
           <t>7167033575-491-684058745078</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>DEXTROSE + SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16446,8 +16918,16 @@
           <t>0824593942-936-956647009322</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16641,8 +17121,16 @@
           <t>7681197963-103-011677018674</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16836,8 +17324,16 @@
           <t>9512919928-150-210624636460</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17031,8 +17527,16 @@
           <t>3494515471-284-634689814408</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17226,8 +17730,16 @@
           <t>3862785105-157-279565709228</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE + SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>DEXTROSE + SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17421,8 +17933,16 @@
           <t>6976664258-837-242116666431</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17616,8 +18136,16 @@
           <t>9187482261-665-119142648039</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17811,8 +18339,16 @@
           <t>1560257581-799-185628771295</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18002,8 +18538,16 @@
           <t>9073409514-299-714566423543</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18197,8 +18741,16 @@
           <t>6480928195-954-666489112839</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18388,8 +18940,16 @@
           <t>6627168287-556-741843472264</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18579,8 +19139,16 @@
           <t>1318027800-012-990345988546</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18774,8 +19342,16 @@
           <t>9775989408-209-553564328911</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18969,8 +19545,16 @@
           <t>5565395054-633-896002657606</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE ,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DEXTROSE ,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19160,8 +19744,16 @@
           <t>6198714375-451-874462093510</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10%+ SOD.CHLORIDE 0.18%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10%+ SOD.CHLORIDE 0.18% detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19351,8 +19943,16 @@
           <t>3500146118-663-820883911328</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10%+N.SALINE INJ</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10%+N.SALINE INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19546,8 +20146,16 @@
           <t>4225859679-192-299479642559</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% IN 0.45% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% IN 0.45% SOD. CHLORIDE INF detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19733,8 +20341,16 @@
           <t>5807499663-228-541107542202</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% IN 0.45% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% IN 0.45% SOD. CHLORIDE INF detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/14/file.xlsx
+++ b/product_upload/packages/14/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22325,7 +22325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22406,40 +22406,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22519,38 +22524,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>329.26</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-04CDB5F12AA3</t>
         </is>
@@ -22630,38 +22640,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>452.65</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-80EEDD35058A</t>
         </is>
@@ -22741,38 +22756,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>454.81</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-051B5F81505B</t>
         </is>
@@ -22852,38 +22872,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>130</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-3CC43E490579</t>
         </is>
@@ -22963,38 +22988,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>45.43</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-A97355E4C837</t>
         </is>
@@ -23074,38 +23104,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>333.14</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-5B35969A6175</t>
         </is>
@@ -23185,38 +23220,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>402.67</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-1BA60D0A1548</t>
         </is>
@@ -23296,38 +23336,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>425.38</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-0836F2B8CB63</t>
         </is>
@@ -23407,38 +23452,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>178.66</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-A318F0F1AAD4</t>
         </is>
@@ -23518,38 +23568,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>243.28</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-1AF8D513017F</t>
         </is>
@@ -23629,38 +23684,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>393.66</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-567917B5C0A9</t>
         </is>
@@ -23740,38 +23800,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>188.69</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-EE0867B1ED6C</t>
         </is>
@@ -23851,38 +23916,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>213.9</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-CA8CDF4B989D</t>
         </is>
@@ -23962,38 +24032,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>209.08</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-B70E08DB07FB</t>
         </is>
@@ -24073,38 +24148,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>118.84</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-AA68F2A443C6</t>
         </is>
@@ -24184,38 +24264,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>498.07</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-4E298F5E2455</t>
         </is>
@@ -24295,38 +24380,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>297.39</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-4753B2AD06A3</t>
         </is>
@@ -24406,38 +24496,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>202.57</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-D0FC4C62AAFD</t>
         </is>
@@ -24517,38 +24612,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>424.41</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-42AC39CB6C72</t>
         </is>
@@ -24628,38 +24728,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>408.51</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-D7205CAFC64A</t>
         </is>
